--- a/Cambios_Baterias_UPS_2026.xlsx
+++ b/Cambios_Baterias_UPS_2026.xlsx
@@ -4954,8 +4954,12 @@
       <c r="H6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="I6" s="17"/>
-      <c r="J6" s="39"/>
+      <c r="I6" s="17">
+        <v>46259</v>
+      </c>
+      <c r="J6" s="39">
+        <v>20</v>
+      </c>
       <c r="K6" s="10"/>
       <c r="L6" s="41"/>
     </row>
@@ -4984,8 +4988,12 @@
       <c r="H7" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="59"/>
-      <c r="J7" s="40"/>
+      <c r="I7" s="59">
+        <v>46251</v>
+      </c>
+      <c r="J7" s="40">
+        <v>20</v>
+      </c>
       <c r="K7" s="68"/>
       <c r="L7" s="51"/>
     </row>
@@ -6464,8 +6472,12 @@
       <c r="H54" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="I54" s="17"/>
-      <c r="J54" s="39"/>
+      <c r="I54" s="17">
+        <v>46251</v>
+      </c>
+      <c r="J54" s="39">
+        <v>20</v>
+      </c>
       <c r="K54" s="10"/>
       <c r="L54" s="41"/>
     </row>
@@ -7802,8 +7814,12 @@
       <c r="H97" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="I97" s="17"/>
-      <c r="J97" s="39"/>
+      <c r="I97" s="17">
+        <v>46247</v>
+      </c>
+      <c r="J97" s="39">
+        <v>20</v>
+      </c>
       <c r="K97" s="10"/>
       <c r="L97" s="41"/>
     </row>
@@ -9122,8 +9138,12 @@
       <c r="H138" s="25" t="s">
         <v>303</v>
       </c>
-      <c r="I138" s="62"/>
-      <c r="J138" s="39"/>
+      <c r="I138" s="62">
+        <v>46262</v>
+      </c>
+      <c r="J138" s="39">
+        <v>16</v>
+      </c>
       <c r="K138" s="10"/>
       <c r="L138" s="41"/>
     </row>
@@ -12496,8 +12516,12 @@
       <c r="H248" s="28" t="s">
         <v>493</v>
       </c>
-      <c r="I248" s="17"/>
-      <c r="J248" s="39"/>
+      <c r="I248" s="17">
+        <v>46290</v>
+      </c>
+      <c r="J248" s="39">
+        <v>16</v>
+      </c>
       <c r="K248" s="10"/>
       <c r="L248" s="41"/>
     </row>
@@ -13024,8 +13048,12 @@
       <c r="H265" s="6" t="s">
         <v>518</v>
       </c>
-      <c r="I265" s="17"/>
-      <c r="J265" s="39"/>
+      <c r="I265" s="17">
+        <v>46248</v>
+      </c>
+      <c r="J265" s="39">
+        <v>6</v>
+      </c>
       <c r="K265" s="16">
         <v>45726</v>
       </c>
@@ -15764,8 +15792,12 @@
       <c r="H353" s="6" t="s">
         <v>684</v>
       </c>
-      <c r="I353" s="17"/>
-      <c r="J353" s="39"/>
+      <c r="I353" s="17">
+        <v>46275</v>
+      </c>
+      <c r="J353" s="39">
+        <v>16</v>
+      </c>
       <c r="K353" s="10">
         <v>45887</v>
       </c>
@@ -16088,8 +16120,12 @@
       <c r="H363" s="6" t="s">
         <v>703</v>
       </c>
-      <c r="I363" s="17"/>
-      <c r="J363" s="39"/>
+      <c r="I363" s="17">
+        <v>46248</v>
+      </c>
+      <c r="J363" s="39">
+        <v>20</v>
+      </c>
       <c r="K363" s="10"/>
       <c r="L363" s="41"/>
     </row>
@@ -17678,8 +17714,12 @@
       <c r="H414" s="6" t="s">
         <v>795</v>
       </c>
-      <c r="I414" s="17"/>
-      <c r="J414" s="39"/>
+      <c r="I414" s="17">
+        <v>46259</v>
+      </c>
+      <c r="J414" s="39">
+        <v>16</v>
+      </c>
       <c r="K414" s="16"/>
       <c r="L414" s="50"/>
     </row>
@@ -18340,8 +18380,12 @@
       <c r="H435" s="9" t="s">
         <v>834</v>
       </c>
-      <c r="I435" s="17"/>
-      <c r="J435" s="39"/>
+      <c r="I435" s="17">
+        <v>46288</v>
+      </c>
+      <c r="J435" s="39">
+        <v>6</v>
+      </c>
       <c r="K435" s="10"/>
       <c r="L435" s="41"/>
     </row>
@@ -18370,8 +18414,12 @@
       <c r="H436" s="9" t="s">
         <v>836</v>
       </c>
-      <c r="I436" s="17"/>
-      <c r="J436" s="39"/>
+      <c r="I436" s="17">
+        <v>46275</v>
+      </c>
+      <c r="J436" s="39">
+        <v>6</v>
+      </c>
       <c r="K436" s="10">
         <v>45994</v>
       </c>
@@ -18404,8 +18452,12 @@
       <c r="H437" s="6" t="s">
         <v>616</v>
       </c>
-      <c r="I437" s="17"/>
-      <c r="J437" s="39"/>
+      <c r="I437" s="17">
+        <v>46248</v>
+      </c>
+      <c r="J437" s="39">
+        <v>6</v>
+      </c>
       <c r="K437" s="10"/>
       <c r="L437" s="41"/>
     </row>

--- a/Cambios_Baterias_UPS_2026.xlsx
+++ b/Cambios_Baterias_UPS_2026.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$I$1:$I$505</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$1:$B$505</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
@@ -20018,8 +20018,12 @@
       <c r="H488" s="9" t="s">
         <v>915</v>
       </c>
-      <c r="I488" s="17"/>
-      <c r="J488" s="39"/>
+      <c r="I488" s="17">
+        <v>46262</v>
+      </c>
+      <c r="J488" s="39">
+        <v>6</v>
+      </c>
       <c r="K488" s="10"/>
       <c r="L488" s="41"/>
     </row>
@@ -20306,7 +20310,7 @@
       <c r="L505" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="I1:I505"/>
+  <autoFilter ref="B1:B505"/>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
